--- a/templates/farmacia_excel_operativo_FH_WO8_v1.xlsx
+++ b/templates/farmacia_excel_operativo_FH_WO8_v1.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_DERMA" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_REUMA" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_DIGESTIVO" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_ONCO" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_CATALOGOS" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_CONFIG_EXPORT_MAP" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="01_DERMA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="02_REUMA" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="03_DIGESTIVO" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="04_ONCO" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="05_CATALOGOS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="99_CONFIG_EXPORT_MAP" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01_DERMA'!$A$1:$BI$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'02_REUMA'!$A$1:$BI$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'03_DIGESTIVO'!$A$1:$BI$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'04_ONCO'!$A$1:$BI$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01_DERMA'!$A$1:$BJ$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'02_REUMA'!$A$1:$BJ$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'03_DIGESTIVO'!$A$1:$BJ$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'04_ONCO'!$A$1:$BJ$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -535,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI4"/>
+  <dimension ref="A1:BJ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -599,6 +599,7 @@
     <col width="18" customWidth="1" min="59" max="59"/>
     <col width="10" customWidth="1" min="60" max="60"/>
     <col width="28" customWidth="1" min="61" max="61"/>
+    <col width="20" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -905,6 +906,11 @@
       <c r="BI1" s="7" t="inlineStr">
         <is>
           <t>observaciones_generales</t>
+        </is>
+      </c>
+      <c r="BJ1" s="7" t="inlineStr">
+        <is>
+          <t>solicitud_id</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1120,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BI1"/>
+  <autoFilter ref="A1:BJ1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1125,7 +1131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI4"/>
+  <dimension ref="A1:BJ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1189,6 +1195,7 @@
     <col width="18" customWidth="1" min="59" max="59"/>
     <col width="10" customWidth="1" min="60" max="60"/>
     <col width="28" customWidth="1" min="61" max="61"/>
+    <col width="20" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1497,6 +1504,11 @@
           <t>observaciones_generales</t>
         </is>
       </c>
+      <c r="BJ1" s="7" t="inlineStr">
+        <is>
+          <t>solicitud_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="F2" t="inlineStr">
@@ -1520,7 +1532,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BI1"/>
+  <autoFilter ref="A1:BJ1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1531,7 +1543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI4"/>
+  <dimension ref="A1:BJ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1595,6 +1607,7 @@
     <col width="18" customWidth="1" min="59" max="59"/>
     <col width="10" customWidth="1" min="60" max="60"/>
     <col width="28" customWidth="1" min="61" max="61"/>
+    <col width="20" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1903,6 +1916,11 @@
           <t>observaciones_generales</t>
         </is>
       </c>
+      <c r="BJ1" s="7" t="inlineStr">
+        <is>
+          <t>solicitud_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="F2" t="inlineStr">
@@ -1926,7 +1944,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BI1"/>
+  <autoFilter ref="A1:BJ1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1937,7 +1955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI4"/>
+  <dimension ref="A1:BJ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2001,6 +2019,7 @@
     <col width="18" customWidth="1" min="59" max="59"/>
     <col width="10" customWidth="1" min="60" max="60"/>
     <col width="28" customWidth="1" min="61" max="61"/>
+    <col width="20" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2309,6 +2328,11 @@
           <t>observaciones_generales</t>
         </is>
       </c>
+      <c r="BJ1" s="7" t="inlineStr">
+        <is>
+          <t>solicitud_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="F2" t="inlineStr">
@@ -2332,7 +2356,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BI1"/>
+  <autoFilter ref="A1:BJ1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2343,7 +2367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G152"/>
+  <dimension ref="A1:G151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2820,419 +2844,445 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>rechazado</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>no_aplica</t>
+          <t>denegado</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>requiere_prebiologico</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="10" t="inlineStr">
-        <is>
-          <t>requiere_prebiologico</t>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
           <t>FALSE</t>
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>tb_estado</t>
+        </is>
+      </c>
+    </row>
     <row r="85">
-      <c r="A85" s="10" t="inlineStr">
-        <is>
-          <t>tb_estado</t>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Negativo</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Negativo</t>
+          <t>Positivo</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Positivo</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>No realizado</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>No realizado</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
           <t>No aplica</t>
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>serologias_estado</t>
+        </is>
+      </c>
+    </row>
     <row r="92">
-      <c r="A92" s="10" t="inlineStr">
-        <is>
-          <t>serologias_estado</t>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Negativo</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Negativo</t>
+          <t>Positivo</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Positivo</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>No realizado</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>No realizado</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
           <t>No aplica</t>
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="10" t="inlineStr">
+        <is>
+          <t>vacunas_estado</t>
+        </is>
+      </c>
+    </row>
     <row r="99">
-      <c r="A99" s="10" t="inlineStr">
-        <is>
-          <t>vacunas_estado</t>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Incompleto</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Incompleto</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
           <t>No aplica</t>
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="10" t="inlineStr">
+        <is>
+          <t>adherencia_morisky</t>
+        </is>
+      </c>
+    </row>
     <row r="105">
-      <c r="A105" s="10" t="inlineStr">
-        <is>
-          <t>adherencia_morisky</t>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Alta</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Baja</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
           <t>No evaluada</t>
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="10" t="inlineStr">
+        <is>
+          <t>hay_efecto_adverso</t>
+        </is>
+      </c>
+    </row>
     <row r="111">
-      <c r="A111" s="10" t="inlineStr">
-        <is>
-          <t>hay_efecto_adverso</t>
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
           <t>FALSE</t>
         </is>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t>ea_gravedad</t>
+        </is>
+      </c>
+    </row>
     <row r="115">
-      <c r="A115" s="10" t="inlineStr">
-        <is>
-          <t>ea_gravedad</t>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Grave</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Grave</t>
+          <t>Moderado</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Moderado</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
           <t>Leve</t>
         </is>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" s="10" t="inlineStr">
+        <is>
+          <t>causalidad_naranjo</t>
+        </is>
+      </c>
+    </row>
     <row r="120">
-      <c r="A120" s="10" t="inlineStr">
-        <is>
-          <t>causalidad_naranjo</t>
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Definitiva</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Definitiva</t>
+          <t>Probable</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Probable</t>
+          <t>Posible</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Posible</t>
+          <t>Dudosa</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Dudosa</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
           <t>No evaluada</t>
         </is>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" s="10" t="inlineStr">
+        <is>
+          <t>causalidad_karch</t>
+        </is>
+      </c>
+    </row>
     <row r="127">
-      <c r="A127" s="10" t="inlineStr">
-        <is>
-          <t>causalidad_karch</t>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Definitiva</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Definitiva</t>
+          <t>Probable</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Probable</t>
+          <t>Posible</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Posible</t>
+          <t>Dudosa</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Dudosa</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
           <t>No evaluada</t>
         </is>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" s="10" t="inlineStr">
+        <is>
+          <t>demo_flag</t>
+        </is>
+      </c>
+    </row>
     <row r="134">
-      <c r="A134" s="10" t="inlineStr">
-        <is>
-          <t>demo_flag</t>
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="9" t="inlineStr">
+        <is>
+          <t>CATÁLOGO DE FÁRMACOS ESPECIALES</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t>marca_nombre_visible</t>
+        </is>
+      </c>
+      <c r="B140" s="11" t="inlineStr">
+        <is>
+          <t>principio_activo</t>
+        </is>
+      </c>
+      <c r="C140" s="11" t="inlineStr">
+        <is>
+          <t>categoria_especial</t>
+        </is>
+      </c>
+      <c r="D140" s="11" t="inlineStr">
+        <is>
+          <t>indicacion_uso</t>
+        </is>
+      </c>
+      <c r="E140" s="11" t="inlineStr">
+        <is>
+          <t>observaciones</t>
+        </is>
+      </c>
+      <c r="F140" s="11" t="inlineStr">
+        <is>
+          <t>fecha_alta_catalogo</t>
+        </is>
+      </c>
+      <c r="G140" s="11" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="8" t="inlineStr">
+        <is>
+          <t>Fármaco en investigación X</t>
+        </is>
+      </c>
+      <c r="B141" s="8" t="inlineStr">
+        <is>
+          <t>Principio activo X</t>
+        </is>
+      </c>
+      <c r="C141" s="8" t="inlineStr">
+        <is>
+          <t>ensayo_clinico</t>
+        </is>
+      </c>
+      <c r="D141" s="8" t="inlineStr">
+        <is>
+          <t>Artritis Reumatoide refractaria</t>
+        </is>
+      </c>
+      <c r="E141" s="8" t="inlineStr">
+        <is>
+          <t>Ensayo fase III - hospital</t>
+        </is>
+      </c>
+      <c r="F141" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G141" s="8" t="inlineStr">
+        <is>
           <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="9" t="inlineStr">
-        <is>
-          <t>CATÁLOGO DE FÁRMACOS ESPECIALES</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="11" t="inlineStr">
-        <is>
-          <t>marca_nombre_visible</t>
-        </is>
-      </c>
-      <c r="B141" s="11" t="inlineStr">
-        <is>
-          <t>principio_activo</t>
-        </is>
-      </c>
-      <c r="C141" s="11" t="inlineStr">
-        <is>
-          <t>categoria_especial</t>
-        </is>
-      </c>
-      <c r="D141" s="11" t="inlineStr">
-        <is>
-          <t>indicacion_uso</t>
-        </is>
-      </c>
-      <c r="E141" s="11" t="inlineStr">
-        <is>
-          <t>observaciones</t>
-        </is>
-      </c>
-      <c r="F141" s="11" t="inlineStr">
-        <is>
-          <t>fecha_alta_catalogo</t>
-        </is>
-      </c>
-      <c r="G141" s="11" t="inlineStr">
-        <is>
-          <t>activo</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="8" t="inlineStr">
         <is>
-          <t>Fármaco en investigación X</t>
-        </is>
-      </c>
-      <c r="B142" s="8" t="inlineStr">
-        <is>
-          <t>Principio activo X</t>
-        </is>
-      </c>
+          <t>Medicamento extranjero Y</t>
+        </is>
+      </c>
+      <c r="B142" s="8" t="inlineStr"/>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>ensayo_clinico</t>
+          <t>medicacion_extranjera</t>
         </is>
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>Artritis Reumatoide refractaria</t>
+          <t>LES</t>
         </is>
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>Ensayo fase III - hospital</t>
+          <t>Importado vía medicamentos extranjeros</t>
         </is>
       </c>
       <c r="F142" s="8" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G142" s="8" t="inlineStr">
@@ -3241,90 +3291,57 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="8" t="inlineStr">
-        <is>
-          <t>Medicamento extranjero Y</t>
-        </is>
-      </c>
-      <c r="B143" s="8" t="inlineStr"/>
-      <c r="C143" s="8" t="inlineStr">
-        <is>
-          <t>medicacion_extranjera</t>
-        </is>
-      </c>
-      <c r="D143" s="8" t="inlineStr">
-        <is>
-          <t>LES</t>
-        </is>
-      </c>
-      <c r="E143" s="8" t="inlineStr">
-        <is>
-          <t>Importado vía medicamentos extranjeros</t>
-        </is>
-      </c>
-      <c r="F143" s="8" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G143" s="8" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+    <row r="144">
+      <c r="A144" s="12" t="inlineStr">
+        <is>
+          <t>Categorías de fármaco especial:</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="12" t="inlineStr">
-        <is>
-          <t>Categorías de fármaco especial:</t>
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>fuera_de_ficha_tecnica</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>fuera_de_ficha_tecnica</t>
+          <t>ensayo_clinico</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ensayo_clinico</t>
+          <t>uso_compasivo</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>uso_compasivo</t>
+          <t>medicacion_extranjera</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>medicacion_extranjera</t>
+          <t>preparacion_especial</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>preparacion_especial</t>
+          <t>pendiente_normalizacion</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
-        <is>
-          <t>pendiente_normalizacion</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
         <is>
           <t>otro</t>
         </is>
